--- a/example_inputs/national_wwtp_example.xlsx
+++ b/example_inputs/national_wwtp_example.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WWTP" sheetId="1" r:id="R827fa454c1644a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WWTP" sheetId="1" r:id="Rde26565158fe4204"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,114 +44,24 @@
   <x:borders count="20">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -303,9 +213,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -461,7 +371,7 @@
         <x:v>Synthetic National WWTP 01</x:v>
       </x:c>
       <x:c r="C2" s="20" t="str">
-        <x:v>Example Province A</x:v>
+        <x:v>Henan</x:v>
       </x:c>
       <x:c r="D2" s="20" t="str">
         <x:v>Example City 1</x:v>
@@ -493,7 +403,7 @@
         <x:v>Synthetic National WWTP 02</x:v>
       </x:c>
       <x:c r="C3" s="20" t="str">
-        <x:v>Example Province A</x:v>
+        <x:v>Henan</x:v>
       </x:c>
       <x:c r="D3" s="20" t="str">
         <x:v>Example City 2</x:v>
@@ -525,7 +435,7 @@
         <x:v>Synthetic National WWTP 03</x:v>
       </x:c>
       <x:c r="C4" s="20" t="str">
-        <x:v>Example Province A</x:v>
+        <x:v>Henan</x:v>
       </x:c>
       <x:c r="D4" s="20" t="str">
         <x:v>Example City 3</x:v>
@@ -557,7 +467,7 @@
         <x:v>Synthetic National WWTP 04</x:v>
       </x:c>
       <x:c r="C5" s="20" t="str">
-        <x:v>Example Province B</x:v>
+        <x:v>Hubei</x:v>
       </x:c>
       <x:c r="D5" s="20" t="str">
         <x:v>Example City 4</x:v>
@@ -589,7 +499,7 @@
         <x:v>Synthetic National WWTP 05</x:v>
       </x:c>
       <x:c r="C6" s="20" t="str">
-        <x:v>Example Province B</x:v>
+        <x:v>Hubei</x:v>
       </x:c>
       <x:c r="D6" s="20" t="str">
         <x:v>Example City 5</x:v>
@@ -621,7 +531,7 @@
         <x:v>Synthetic National WWTP 06</x:v>
       </x:c>
       <x:c r="C7" s="20" t="str">
-        <x:v>Example Province B</x:v>
+        <x:v>Hubei</x:v>
       </x:c>
       <x:c r="D7" s="20" t="str">
         <x:v>Example City 6</x:v>
@@ -653,7 +563,7 @@
         <x:v>Synthetic National WWTP 07</x:v>
       </x:c>
       <x:c r="C8" s="20" t="str">
-        <x:v>Example Province C</x:v>
+        <x:v>Jiangxi</x:v>
       </x:c>
       <x:c r="D8" s="20" t="str">
         <x:v>Example City 7</x:v>
@@ -685,7 +595,7 @@
         <x:v>Synthetic National WWTP 08</x:v>
       </x:c>
       <x:c r="C9" s="20" t="str">
-        <x:v>Example Province C</x:v>
+        <x:v>Jiangxi</x:v>
       </x:c>
       <x:c r="D9" s="20" t="str">
         <x:v>Example City 8</x:v>
@@ -717,7 +627,7 @@
         <x:v>Synthetic National WWTP 09</x:v>
       </x:c>
       <x:c r="C10" s="20" t="str">
-        <x:v>Example Province C</x:v>
+        <x:v>Jiangxi</x:v>
       </x:c>
       <x:c r="D10" s="20" t="str">
         <x:v>Example City 9</x:v>
@@ -749,7 +659,7 @@
         <x:v>Synthetic National WWTP 10</x:v>
       </x:c>
       <x:c r="C11" s="23" t="str">
-        <x:v>Example Province D</x:v>
+        <x:v>Hebei</x:v>
       </x:c>
       <x:c r="D11" s="23" t="str">
         <x:v>Example City 10</x:v>
